--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D280"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5466,6 +5466,24 @@
       <c r="D280" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>395.54</v>
+      </c>
+      <c r="C281" t="n">
+        <v>433.37</v>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B297"/>
+  <dimension ref="A1:B298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8453,6 +8471,16 @@
       </c>
       <c r="B297" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>0.99</v>
       </c>
     </row>
   </sheetData>
@@ -8621,28 +8649,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07010452738287087</v>
+        <v>-0.06979649977592943</v>
       </c>
       <c r="J2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K2" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03160352582278392</v>
+        <v>0.03159747081542363</v>
       </c>
       <c r="M2" t="n">
-        <v>2.360660753561372</v>
+        <v>2.353732393739224</v>
       </c>
       <c r="N2" t="n">
-        <v>8.996378633202051</v>
+        <v>8.964902058456943</v>
       </c>
       <c r="O2" t="n">
-        <v>2.99939637814045</v>
+        <v>2.994144628847602</v>
       </c>
       <c r="P2" t="n">
-        <v>396.9515542496121</v>
+        <v>396.9486952277454</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8699,28 +8727,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.26227059155798</v>
+        <v>0.2625077696516758</v>
       </c>
       <c r="J3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07578149613842977</v>
+        <v>0.07652559896607936</v>
       </c>
       <c r="M3" t="n">
-        <v>5.331370284839626</v>
+        <v>5.313279738725623</v>
       </c>
       <c r="N3" t="n">
-        <v>48.85748883533866</v>
+        <v>48.68148159022575</v>
       </c>
       <c r="O3" t="n">
-        <v>6.989813218916415</v>
+        <v>6.977211591332583</v>
       </c>
       <c r="P3" t="n">
-        <v>426.1438822298421</v>
+        <v>426.1416299039347</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8758,7 +8786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D280"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14909,6 +14937,28 @@
         </is>
       </c>
     </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:17:51+00:00</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>-34.72569613188248,173.0938993455152</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>-34.72533568887116,173.09478620549893</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5482,6 +5482,42 @@
         <v>433.37</v>
       </c>
       <c r="D281" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>394.09</v>
+      </c>
+      <c r="C282" t="n">
+        <v>429.4</v>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>392.6</v>
+      </c>
+      <c r="C283" t="n">
+        <v>429.58</v>
+      </c>
+      <c r="D283" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -5498,7 +5534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B298"/>
+  <dimension ref="A1:B300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8481,6 +8517,26 @@
       </c>
       <c r="B298" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>
@@ -8649,28 +8705,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06979649977592943</v>
+        <v>-0.07227544751255729</v>
       </c>
       <c r="J2" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K2" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03159747081542363</v>
+        <v>0.03427553872469236</v>
       </c>
       <c r="M2" t="n">
-        <v>2.353732393739224</v>
+        <v>2.349531534476856</v>
       </c>
       <c r="N2" t="n">
-        <v>8.964902058456943</v>
+        <v>8.926747503201153</v>
       </c>
       <c r="O2" t="n">
-        <v>2.994144628847602</v>
+        <v>2.987766306658061</v>
       </c>
       <c r="P2" t="n">
-        <v>396.9486952277454</v>
+        <v>396.971787195394</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8727,28 +8783,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2625077696516758</v>
+        <v>0.2573598655636306</v>
       </c>
       <c r="J3" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K3" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07652559896607936</v>
+        <v>0.07483965629783329</v>
       </c>
       <c r="M3" t="n">
-        <v>5.313279738725623</v>
+        <v>5.300799501885079</v>
       </c>
       <c r="N3" t="n">
-        <v>48.68148159022575</v>
+        <v>48.42206465610426</v>
       </c>
       <c r="O3" t="n">
-        <v>6.977211591332583</v>
+        <v>6.958596457339961</v>
       </c>
       <c r="P3" t="n">
-        <v>426.1416299039347</v>
+        <v>426.1906782059416</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8786,7 +8842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14959,6 +15015,50 @@
         </is>
       </c>
     </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>-34.725709203001614,173.09389977237578</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>-34.72537147668988,173.0947873744541</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>-34.72572263470331,173.0939002110119</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>-34.72536985406837,173.09478732145362</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5520,6 +5520,42 @@
       <c r="D283" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>389.78</v>
+      </c>
+      <c r="C284" t="n">
+        <v>432.55</v>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>390.27</v>
+      </c>
+      <c r="C285" t="n">
+        <v>432.47</v>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B300"/>
+  <dimension ref="A1:B302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8537,6 +8573,26 @@
       </c>
       <c r="B300" t="n">
         <v>0.91</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -8705,28 +8761,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07227544751255729</v>
+        <v>-0.07927444055115196</v>
       </c>
       <c r="J2" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K2" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03427553872469236</v>
+        <v>0.04085914898154619</v>
       </c>
       <c r="M2" t="n">
-        <v>2.349531534476856</v>
+        <v>2.367546819432881</v>
       </c>
       <c r="N2" t="n">
-        <v>8.926747503201153</v>
+        <v>9.038038837631193</v>
       </c>
       <c r="O2" t="n">
-        <v>2.987766306658061</v>
+        <v>3.006333121533805</v>
       </c>
       <c r="P2" t="n">
-        <v>396.971787195394</v>
+        <v>397.0374730646113</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8783,28 +8839,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2573598655636306</v>
+        <v>0.2566220778329603</v>
       </c>
       <c r="J3" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K3" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07483965629783329</v>
+        <v>0.07564249633361486</v>
       </c>
       <c r="M3" t="n">
-        <v>5.300799501885079</v>
+        <v>5.266731412949302</v>
       </c>
       <c r="N3" t="n">
-        <v>48.42206465610426</v>
+        <v>48.07930234053426</v>
       </c>
       <c r="O3" t="n">
-        <v>6.958596457339961</v>
+        <v>6.933924021831668</v>
       </c>
       <c r="P3" t="n">
-        <v>426.1906782059416</v>
+        <v>426.1977622313745</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8842,7 +8898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D283"/>
+  <dimension ref="A1:D285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15059,6 +15115,50 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>-34.72574805577626,173.0939010411828</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>-34.725343080813595,173.0947864469455</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:17:31+00:00</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>-34.725743638639464,173.09390089693318</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>-34.725343801978696,173.09478647050128</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D285"/>
+  <dimension ref="A1:D287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5554,6 +5554,42 @@
         <v>432.47</v>
       </c>
       <c r="D285" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>389.74</v>
+      </c>
+      <c r="C286" t="n">
+        <v>434.01</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>390.2</v>
+      </c>
+      <c r="C287" t="n">
+        <v>432.57</v>
+      </c>
+      <c r="D287" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5570,7 +5606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8593,6 +8629,26 @@
       </c>
       <c r="B302" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -8761,28 +8817,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07927444055115196</v>
+        <v>-0.08605956666454077</v>
       </c>
       <c r="J2" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K2" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04085914898154619</v>
+        <v>0.04772685874362081</v>
       </c>
       <c r="M2" t="n">
-        <v>2.367546819432881</v>
+        <v>2.384892631698968</v>
       </c>
       <c r="N2" t="n">
-        <v>9.038038837631193</v>
+        <v>9.1428658008518</v>
       </c>
       <c r="O2" t="n">
-        <v>3.006333121533805</v>
+        <v>3.023717215754774</v>
       </c>
       <c r="P2" t="n">
-        <v>397.0374730646113</v>
+        <v>397.1013984676528</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8839,28 +8895,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2566220778329603</v>
+        <v>0.2569804404075174</v>
       </c>
       <c r="J3" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K3" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07564249633361486</v>
+        <v>0.07703388194568206</v>
       </c>
       <c r="M3" t="n">
-        <v>5.266731412949302</v>
+        <v>5.234659110821092</v>
       </c>
       <c r="N3" t="n">
-        <v>48.07930234053426</v>
+        <v>47.74372111959626</v>
       </c>
       <c r="O3" t="n">
-        <v>6.933924021831668</v>
+        <v>6.909683141765349</v>
       </c>
       <c r="P3" t="n">
-        <v>426.1977622313745</v>
+        <v>426.1943229284701</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8898,7 +8954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D285"/>
+  <dimension ref="A1:D287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15159,6 +15215,50 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:17:16+00:00</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>-34.72574841635883,173.09390105295824</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>-34.72532991955024,173.09478601705285</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:17:21+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>-34.72574426965901,173.09390091754028</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>-34.72534290052231,173.09478644105656</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D287"/>
+  <dimension ref="A1:D289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5592,6 +5592,42 @@
       <c r="D287" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>390.64</v>
+      </c>
+      <c r="C288" t="n">
+        <v>432.16</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>390.69</v>
+      </c>
+      <c r="C289" t="n">
+        <v>435.02</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B304"/>
+  <dimension ref="A1:B306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8649,6 +8685,26 @@
       </c>
       <c r="B304" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -8817,28 +8873,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08605956666454077</v>
+        <v>-0.09163133663553186</v>
       </c>
       <c r="J2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K2" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04772685874362081</v>
+        <v>0.0539590403651361</v>
       </c>
       <c r="M2" t="n">
-        <v>2.384892631698968</v>
+        <v>2.39595428502124</v>
       </c>
       <c r="N2" t="n">
-        <v>9.1428658008518</v>
+        <v>9.195595341938478</v>
       </c>
       <c r="O2" t="n">
-        <v>3.023717215754774</v>
+        <v>3.03242400431379</v>
       </c>
       <c r="P2" t="n">
-        <v>397.1013984676528</v>
+        <v>397.1540745028075</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8895,28 +8951,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2569804404075174</v>
+        <v>0.2577099900431385</v>
       </c>
       <c r="J3" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="K3" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07703388194568206</v>
+        <v>0.0786164576384939</v>
       </c>
       <c r="M3" t="n">
-        <v>5.234659110821092</v>
+        <v>5.207982084445591</v>
       </c>
       <c r="N3" t="n">
-        <v>47.74372111959626</v>
+        <v>47.42482980607971</v>
       </c>
       <c r="O3" t="n">
-        <v>6.909683141765349</v>
+        <v>6.886568797745341</v>
       </c>
       <c r="P3" t="n">
-        <v>426.1943229284701</v>
+        <v>426.1872507506963</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -8954,7 +9010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D287"/>
+  <dimension ref="A1:D289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15259,6 +15315,50 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>-34.725740303250475,173.09390078801005</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>-34.72534659649351,173.0947865617799</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>-34.72573985252224,173.0939007732907</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>-34.72532081484065,173.09478571966145</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D289"/>
+  <dimension ref="A1:D290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5628,6 +5628,24 @@
       <c r="D289" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>390.89</v>
+      </c>
+      <c r="C290" t="n">
+        <v>434.94</v>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B306"/>
+  <dimension ref="A1:B307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8705,6 +8723,16 @@
       </c>
       <c r="B306" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -8873,28 +8901,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09163133663553186</v>
+        <v>-0.09418480214478474</v>
       </c>
       <c r="J2" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K2" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0539590403651361</v>
+        <v>0.05698524389667581</v>
       </c>
       <c r="M2" t="n">
-        <v>2.39595428502124</v>
+        <v>2.400351283908992</v>
       </c>
       <c r="N2" t="n">
-        <v>9.195595341938478</v>
+        <v>9.213444966873407</v>
       </c>
       <c r="O2" t="n">
-        <v>3.03242400431379</v>
+        <v>3.035365705623197</v>
       </c>
       <c r="P2" t="n">
-        <v>397.1540745028075</v>
+        <v>397.1783099830076</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8951,28 +8979,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2577099900431385</v>
+        <v>0.2589756397858153</v>
       </c>
       <c r="J3" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0786164576384939</v>
+        <v>0.079918470769061</v>
       </c>
       <c r="M3" t="n">
-        <v>5.207982084445591</v>
+        <v>5.19629567659247</v>
       </c>
       <c r="N3" t="n">
-        <v>47.42482980607971</v>
+        <v>47.27078785669648</v>
       </c>
       <c r="O3" t="n">
-        <v>6.886568797745341</v>
+        <v>6.875375470234078</v>
       </c>
       <c r="P3" t="n">
-        <v>426.1872507506963</v>
+        <v>426.1749665411666</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9010,7 +9038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D289"/>
+  <dimension ref="A1:D290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15359,6 +15387,28 @@
         </is>
       </c>
     </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>-34.725738049609255,173.09390071441334</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>-34.725321536005765,173.0947857432172</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
